--- a/data/data_ml_tax.xlsx
+++ b/data/data_ml_tax.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11880" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11880" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="PIT" sheetId="7" r:id="rId1"/>

--- a/data/data_ml_tax.xlsx
+++ b/data/data_ml_tax.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DOSYALAR\2026-2029 bütçe\Yapay Zeka\python_model\MM_GelirButce\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workstation\gelirbutce\MM_GelirButce\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11880" activeTab="5"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11880" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="PIT" sheetId="7" r:id="rId1"/>
@@ -20,7 +20,7 @@
     <sheet name="Tobacco SCT" sheetId="4" r:id="rId6"/>
     <sheet name="Motor Vehicles SCT" sheetId="5" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -33,105 +33,6 @@
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="68">
   <si>
     <t>Period</t>
-  </si>
-  <si>
-    <t>2020 Ç1</t>
-  </si>
-  <si>
-    <t>2020 Ç2</t>
-  </si>
-  <si>
-    <t>2020 Ç3</t>
-  </si>
-  <si>
-    <t>2020 Ç4</t>
-  </si>
-  <si>
-    <t>2021 Ç1</t>
-  </si>
-  <si>
-    <t>2021 Ç2</t>
-  </si>
-  <si>
-    <t>2021 Ç3</t>
-  </si>
-  <si>
-    <t>2021 Ç4</t>
-  </si>
-  <si>
-    <t>2022 Ç1</t>
-  </si>
-  <si>
-    <t>2022 Ç2</t>
-  </si>
-  <si>
-    <t>2022 Ç3</t>
-  </si>
-  <si>
-    <t>2022 Ç4</t>
-  </si>
-  <si>
-    <t>2023 Ç1</t>
-  </si>
-  <si>
-    <t>2023 Ç2</t>
-  </si>
-  <si>
-    <t>2023 Ç3</t>
-  </si>
-  <si>
-    <t>2023 Ç4</t>
-  </si>
-  <si>
-    <t>2024 Ç1</t>
-  </si>
-  <si>
-    <t>2024 Ç2</t>
-  </si>
-  <si>
-    <t>2024 Ç3</t>
-  </si>
-  <si>
-    <t>2024 Ç4</t>
-  </si>
-  <si>
-    <t>2025 Ç1</t>
-  </si>
-  <si>
-    <t>2025 Ç2</t>
-  </si>
-  <si>
-    <t>2025 Ç3</t>
-  </si>
-  <si>
-    <t>2025 Ç4</t>
-  </si>
-  <si>
-    <t>2026 Ç1</t>
-  </si>
-  <si>
-    <t>2018 Ç1</t>
-  </si>
-  <si>
-    <t>2019 Ç2</t>
-  </si>
-  <si>
-    <t>2019 Ç1</t>
-  </si>
-  <si>
-    <t>2018 Ç2</t>
-  </si>
-  <si>
-    <t>2019 Ç3</t>
-  </si>
-  <si>
-    <t>2019 Ç4</t>
-  </si>
-  <si>
-    <t>2018 Ç3</t>
-  </si>
-  <si>
-    <t>2018 Ç4</t>
   </si>
   <si>
     <t>Cons_Diesel</t>
@@ -235,11 +136,110 @@
   <si>
     <t>CreditCart_Usage_Vol</t>
   </si>
+  <si>
+    <t>2018Q1</t>
+  </si>
+  <si>
+    <t>2018Q2</t>
+  </si>
+  <si>
+    <t>2018Q3</t>
+  </si>
+  <si>
+    <t>2018Q4</t>
+  </si>
+  <si>
+    <t>2019Q1</t>
+  </si>
+  <si>
+    <t>2019Q2</t>
+  </si>
+  <si>
+    <t>2019Q3</t>
+  </si>
+  <si>
+    <t>2019Q4</t>
+  </si>
+  <si>
+    <t>2020Q1</t>
+  </si>
+  <si>
+    <t>2020Q2</t>
+  </si>
+  <si>
+    <t>2020Q3</t>
+  </si>
+  <si>
+    <t>2020Q4</t>
+  </si>
+  <si>
+    <t>2021Q1</t>
+  </si>
+  <si>
+    <t>2021Q2</t>
+  </si>
+  <si>
+    <t>2021Q3</t>
+  </si>
+  <si>
+    <t>2021Q4</t>
+  </si>
+  <si>
+    <t>2022Q1</t>
+  </si>
+  <si>
+    <t>2022Q2</t>
+  </si>
+  <si>
+    <t>2022Q3</t>
+  </si>
+  <si>
+    <t>2022Q4</t>
+  </si>
+  <si>
+    <t>2023Q1</t>
+  </si>
+  <si>
+    <t>2023Q2</t>
+  </si>
+  <si>
+    <t>2023Q3</t>
+  </si>
+  <si>
+    <t>2023Q4</t>
+  </si>
+  <si>
+    <t>2024Q1</t>
+  </si>
+  <si>
+    <t>2024Q2</t>
+  </si>
+  <si>
+    <t>2024Q3</t>
+  </si>
+  <si>
+    <t>2024Q4</t>
+  </si>
+  <si>
+    <t>2025Q1</t>
+  </si>
+  <si>
+    <t>2025Q2</t>
+  </si>
+  <si>
+    <t>2025Q3</t>
+  </si>
+  <si>
+    <t>2025Q4</t>
+  </si>
+  <si>
+    <t>2026Q1</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -688,35 +688,35 @@
     <tabColor rgb="FFFFC000"/>
   </sheetPr>
   <dimension ref="A1:W53"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="6" width="18" customWidth="1"/>
-    <col min="7" max="7" width="16.7109375" customWidth="1"/>
+    <col min="7" max="7" width="16.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="18" t="s">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="C1" s="18" t="s">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="D1" s="18" t="s">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="E1" s="18" t="s">
-        <v>38</v>
+        <v>5</v>
       </c>
       <c r="F1" s="18" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="19" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="B2" s="20">
         <v>27151.641</v>
@@ -734,9 +734,9 @@
         <v>12.428749999999999</v>
       </c>
     </row>
-    <row r="3" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="19" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="B3" s="20">
         <v>31173.8</v>
@@ -754,9 +754,9 @@
         <v>13.558583333333333</v>
       </c>
     </row>
-    <row r="4" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="19" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="B4" s="20">
         <v>32933.004000000001</v>
@@ -774,9 +774,9 @@
         <v>18.788083333333333</v>
       </c>
     </row>
-    <row r="5" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A5" s="19" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="B5" s="20">
         <v>37844.142999999996</v>
@@ -794,9 +794,9 @@
         <v>23.156750000000002</v>
       </c>
     </row>
-    <row r="6" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A6" s="19" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="B6" s="20">
         <v>32359.993999999999</v>
@@ -814,9 +814,9 @@
         <v>20.396583333333336</v>
       </c>
     </row>
-    <row r="7" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A7" s="19" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="B7" s="20">
         <v>36644.006999999998</v>
@@ -834,9 +834,9 @@
         <v>21.944500000000001</v>
       </c>
     </row>
-    <row r="8" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A8" s="19" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="B8" s="20">
         <v>38362.739000000001</v>
@@ -854,9 +854,9 @@
         <v>18.347916666666666</v>
       </c>
     </row>
-    <row r="9" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A9" s="19" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="B9" s="20">
         <v>44422.53</v>
@@ -874,9 +874,9 @@
         <v>12.05325</v>
       </c>
     </row>
-    <row r="10" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A10" s="19" t="s">
-        <v>1</v>
+        <v>43</v>
       </c>
       <c r="B10" s="20">
         <v>35458.731</v>
@@ -894,9 +894,9 @@
         <v>10.840428939394002</v>
       </c>
     </row>
-    <row r="11" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A11" s="19" t="s">
-        <v>2</v>
+        <v>44</v>
       </c>
       <c r="B11" s="20">
         <v>25942.071</v>
@@ -914,9 +914,9 @@
         <v>8.520102100840333</v>
       </c>
     </row>
-    <row r="12" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A12" s="19" t="s">
-        <v>3</v>
+        <v>45</v>
       </c>
       <c r="B12" s="20">
         <v>38016.527000000002</v>
@@ -934,9 +934,9 @@
         <v>9.5180088167389663</v>
       </c>
     </row>
-    <row r="13" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A13" s="19" t="s">
-        <v>4</v>
+        <v>46</v>
       </c>
       <c r="B13" s="20">
         <v>47833.703000000001</v>
@@ -954,9 +954,9 @@
         <v>14.512560524499667</v>
       </c>
     </row>
-    <row r="14" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A14" s="19" t="s">
-        <v>5</v>
+        <v>47</v>
       </c>
       <c r="B14" s="20">
         <v>40891.688999999998</v>
@@ -974,9 +974,9 @@
         <v>17.317593695652334</v>
       </c>
     </row>
-    <row r="15" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A15" s="19" t="s">
-        <v>6</v>
+        <v>48</v>
       </c>
       <c r="B15" s="20">
         <v>44415.381999999998</v>
@@ -994,9 +994,9 @@
         <v>19.035284439634665</v>
       </c>
     </row>
-    <row r="16" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A16" s="19" t="s">
-        <v>7</v>
+        <v>49</v>
       </c>
       <c r="B16" s="20">
         <v>50086.545999999995</v>
@@ -1014,9 +1014,9 @@
         <v>18.913132459044334</v>
       </c>
     </row>
-    <row r="17" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A17" s="19" t="s">
-        <v>8</v>
+        <v>50</v>
       </c>
       <c r="B17" s="20">
         <v>65974.653000000006</v>
@@ -1034,9 +1034,9 @@
         <v>16.235726429512667</v>
       </c>
     </row>
-    <row r="18" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A18" s="19" t="s">
-        <v>9</v>
+        <v>51</v>
       </c>
       <c r="B18" s="20">
         <v>58026.015000000007</v>
@@ -1054,9 +1054,9 @@
         <v>14.171846749482333</v>
       </c>
     </row>
-    <row r="19" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A19" s="19" t="s">
-        <v>10</v>
+        <v>52</v>
       </c>
       <c r="B19" s="20">
         <v>67513.22</v>
@@ -1074,9 +1074,9 @@
         <v>14.1283266064</v>
       </c>
     </row>
-    <row r="20" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A20" s="19" t="s">
-        <v>11</v>
+        <v>53</v>
       </c>
       <c r="B20" s="20">
         <v>89438.934999999998</v>
@@ -1094,9 +1094,9 @@
         <v>13.640888143338332</v>
       </c>
     </row>
-    <row r="21" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A21" s="19" t="s">
-        <v>12</v>
+        <v>54</v>
       </c>
       <c r="B21" s="20">
         <v>114181.64597302997</v>
@@ -1114,9 +1114,9 @@
         <v>10.707056275917033</v>
       </c>
     </row>
-    <row r="22" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A22" s="19" t="s">
-        <v>13</v>
+        <v>55</v>
       </c>
       <c r="B22" s="20">
         <v>147832.25184114138</v>
@@ -1134,9 +1134,9 @@
         <v>9.0238702715121342</v>
       </c>
     </row>
-    <row r="23" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A23" s="19" t="s">
-        <v>14</v>
+        <v>56</v>
       </c>
       <c r="B23" s="20">
         <v>142935.25975939864</v>
@@ -1154,9 +1154,9 @@
         <v>10.110375104427634</v>
       </c>
     </row>
-    <row r="24" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A24" s="19" t="s">
-        <v>15</v>
+        <v>57</v>
       </c>
       <c r="B24" s="20">
         <v>179720.55298605</v>
@@ -1174,9 +1174,9 @@
         <v>20.396573809523666</v>
       </c>
     </row>
-    <row r="25" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A25" s="19" t="s">
-        <v>16</v>
+        <v>58</v>
       </c>
       <c r="B25" s="20">
         <v>221537.87753383</v>
@@ -1194,9 +1194,9 @@
         <v>35.676486147186331</v>
       </c>
     </row>
-    <row r="26" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A26" s="19" t="s">
-        <v>17</v>
+        <v>59</v>
       </c>
       <c r="B26" s="20">
         <v>246918.04026819477</v>
@@ -1214,9 +1214,9 @@
         <v>45.418018614718669</v>
       </c>
     </row>
-    <row r="27" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A27" s="19" t="s">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="B27" s="20">
         <v>218928.70072644521</v>
@@ -1234,9 +1234,9 @@
         <v>51.324886419340338</v>
       </c>
     </row>
-    <row r="28" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A28" s="19" t="s">
-        <v>19</v>
+        <v>61</v>
       </c>
       <c r="B28" s="20">
         <v>206223.53374473998</v>
@@ -1254,9 +1254,9 @@
         <v>50.333264548872336</v>
       </c>
     </row>
-    <row r="29" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A29" s="19" t="s">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="B29" s="20">
         <v>218127.76050577994</v>
@@ -1274,9 +1274,9 @@
         <v>49.255071060606006</v>
       </c>
     </row>
-    <row r="30" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A30" s="19" t="s">
-        <v>21</v>
+        <v>63</v>
       </c>
       <c r="B30" s="20">
         <v>265634.0856500052</v>
@@ -1294,9 +1294,9 @@
         <v>44.841679473684337</v>
       </c>
     </row>
-    <row r="31" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A31" s="19" t="s">
-        <v>22</v>
+        <v>64</v>
       </c>
       <c r="B31" s="20">
         <v>273268.4265593348</v>
@@ -1314,9 +1314,9 @@
         <v>47.846294035087659</v>
       </c>
     </row>
-    <row r="32" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A32" s="19" t="s">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="B32" s="22">
         <v>721363.04416252999</v>
@@ -1334,9 +1334,9 @@
         <v>43.03166560606067</v>
       </c>
     </row>
-    <row r="33" spans="1:23" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:23" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A33" s="19" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="B33" s="20">
         <v>839594.49351406004</v>
@@ -1354,9 +1354,9 @@
         <v>39.232901014492668</v>
       </c>
     </row>
-    <row r="34" spans="1:23" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:23" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A34" s="19" t="s">
-        <v>25</v>
+        <v>67</v>
       </c>
       <c r="B34" s="20">
         <v>752690.57309392991</v>
@@ -1374,7 +1374,7 @@
         <v>38.088014445396823</v>
       </c>
     </row>
-    <row r="35" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:23" x14ac:dyDescent="0.3">
       <c r="H35" s="6"/>
       <c r="I35" s="6"/>
       <c r="J35" s="6"/>
@@ -1392,7 +1392,7 @@
       <c r="V35" s="6"/>
       <c r="W35" s="6"/>
     </row>
-    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:23" x14ac:dyDescent="0.3">
       <c r="H36" s="6"/>
       <c r="I36" s="6"/>
       <c r="J36" s="6"/>
@@ -1410,7 +1410,7 @@
       <c r="V36" s="6"/>
       <c r="W36" s="6"/>
     </row>
-    <row r="37" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:23" x14ac:dyDescent="0.3">
       <c r="H37" s="6"/>
       <c r="I37" s="6"/>
       <c r="J37" s="6"/>
@@ -1428,7 +1428,7 @@
       <c r="V37" s="6"/>
       <c r="W37" s="6"/>
     </row>
-    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:23" x14ac:dyDescent="0.3">
       <c r="H38" s="6"/>
       <c r="I38" s="6"/>
       <c r="J38" s="6"/>
@@ -1446,7 +1446,7 @@
       <c r="V38" s="6"/>
       <c r="W38" s="6"/>
     </row>
-    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:23" x14ac:dyDescent="0.3">
       <c r="H39" s="6"/>
       <c r="I39" s="6"/>
       <c r="J39" s="6"/>
@@ -1464,7 +1464,7 @@
       <c r="V39" s="6"/>
       <c r="W39" s="6"/>
     </row>
-    <row r="40" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:23" x14ac:dyDescent="0.3">
       <c r="H40" s="6"/>
       <c r="I40" s="6"/>
       <c r="J40" s="6"/>
@@ -1482,7 +1482,7 @@
       <c r="V40" s="6"/>
       <c r="W40" s="6"/>
     </row>
-    <row r="41" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:23" x14ac:dyDescent="0.3">
       <c r="H41" s="6"/>
       <c r="I41" s="6"/>
       <c r="J41" s="6"/>
@@ -1500,7 +1500,7 @@
       <c r="V41" s="6"/>
       <c r="W41" s="6"/>
     </row>
-    <row r="42" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:23" x14ac:dyDescent="0.3">
       <c r="H42" s="6"/>
       <c r="I42" s="6"/>
       <c r="J42" s="6"/>
@@ -1518,7 +1518,7 @@
       <c r="V42" s="6"/>
       <c r="W42" s="6"/>
     </row>
-    <row r="43" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:23" x14ac:dyDescent="0.3">
       <c r="H43" s="6"/>
       <c r="I43" s="6"/>
       <c r="J43" s="6"/>
@@ -1536,34 +1536,34 @@
       <c r="V43" s="6"/>
       <c r="W43" s="6"/>
     </row>
-    <row r="44" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:23" x14ac:dyDescent="0.3">
       <c r="K44" s="6"/>
     </row>
-    <row r="45" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:23" x14ac:dyDescent="0.3">
       <c r="K45" s="6"/>
     </row>
-    <row r="46" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:23" x14ac:dyDescent="0.3">
       <c r="K46" s="6"/>
     </row>
-    <row r="47" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:23" x14ac:dyDescent="0.3">
       <c r="K47" s="6"/>
     </row>
-    <row r="48" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:23" x14ac:dyDescent="0.3">
       <c r="K48" s="6"/>
     </row>
-    <row r="49" spans="11:11" x14ac:dyDescent="0.25">
+    <row r="49" spans="11:11" x14ac:dyDescent="0.3">
       <c r="K49" s="6"/>
     </row>
-    <row r="50" spans="11:11" x14ac:dyDescent="0.25">
+    <row r="50" spans="11:11" x14ac:dyDescent="0.3">
       <c r="K50" s="6"/>
     </row>
-    <row r="51" spans="11:11" x14ac:dyDescent="0.25">
+    <row r="51" spans="11:11" x14ac:dyDescent="0.3">
       <c r="K51" s="6"/>
     </row>
-    <row r="52" spans="11:11" x14ac:dyDescent="0.25">
+    <row r="52" spans="11:11" x14ac:dyDescent="0.3">
       <c r="K52" s="6"/>
     </row>
-    <row r="53" spans="11:11" x14ac:dyDescent="0.25">
+    <row r="53" spans="11:11" x14ac:dyDescent="0.3">
       <c r="K53" s="6"/>
     </row>
   </sheetData>
@@ -1578,38 +1578,38 @@
     <tabColor rgb="FFFFC000"/>
   </sheetPr>
   <dimension ref="A1:S141"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="6" width="19.140625" customWidth="1"/>
-    <col min="7" max="7" width="19.140625" style="6" customWidth="1"/>
-    <col min="8" max="8" width="19.140625" customWidth="1"/>
-    <col min="9" max="10" width="16.7109375" customWidth="1"/>
+    <col min="2" max="6" width="19.109375" customWidth="1"/>
+    <col min="7" max="7" width="19.109375" style="6" customWidth="1"/>
+    <col min="8" max="8" width="19.109375" customWidth="1"/>
+    <col min="9" max="10" width="16.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="C1" s="16" t="s">
-        <v>66</v>
+        <v>33</v>
       </c>
       <c r="D1" s="16" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="E1" s="16" t="s">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="F1" s="16" t="s">
-        <v>44</v>
+        <v>11</v>
       </c>
       <c r="G1" s="16" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="H1" s="16" t="s">
-        <v>46</v>
+        <v>13</v>
       </c>
       <c r="I1" s="3"/>
       <c r="L1" s="6"/>
@@ -1621,9 +1621,9 @@
       <c r="R1" s="6"/>
       <c r="S1" s="6"/>
     </row>
-    <row r="2" spans="1:19" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="15" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="B2" s="4">
         <v>16774091</v>
@@ -1647,9 +1647,9 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:19" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="15" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="B3" s="4">
         <v>17956097</v>
@@ -1673,9 +1673,9 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:19" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="15" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="B4" s="4">
         <v>18120291</v>
@@ -1699,9 +1699,9 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:19" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A5" s="15" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="B5" s="4">
         <v>25822835</v>
@@ -1725,9 +1725,9 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:19" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A6" s="15" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="B6" s="4">
         <v>20689252</v>
@@ -1751,9 +1751,9 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:19" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A7" s="15" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="B7" s="4">
         <v>15831806</v>
@@ -1777,9 +1777,9 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:19" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A8" s="15" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="B8" s="4">
         <v>18919907</v>
@@ -1803,9 +1803,9 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:19" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A9" s="15" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="B9" s="4">
         <v>23388018</v>
@@ -1829,9 +1829,9 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:19" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A10" s="15" t="s">
-        <v>1</v>
+        <v>43</v>
       </c>
       <c r="B10" s="4">
         <v>27069100</v>
@@ -1855,9 +1855,9 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:19" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:19" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A11" s="15" t="s">
-        <v>2</v>
+        <v>44</v>
       </c>
       <c r="B11" s="4">
         <v>22231634</v>
@@ -1881,9 +1881,9 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:19" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:19" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A12" s="15" t="s">
-        <v>3</v>
+        <v>45</v>
       </c>
       <c r="B12" s="4">
         <v>29304677</v>
@@ -1907,9 +1907,9 @@
         <v>22</v>
       </c>
     </row>
-    <row r="13" spans="1:19" s="6" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:19" s="6" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="15" t="s">
-        <v>4</v>
+        <v>46</v>
       </c>
       <c r="B13" s="4">
         <v>26441962</v>
@@ -1933,9 +1933,9 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:19" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:19" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A14" s="15" t="s">
-        <v>5</v>
+        <v>47</v>
       </c>
       <c r="B14" s="4">
         <v>39989259</v>
@@ -1959,9 +1959,9 @@
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:19" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:19" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A15" s="15" t="s">
-        <v>6</v>
+        <v>48</v>
       </c>
       <c r="B15" s="4">
         <v>29557126</v>
@@ -1985,9 +1985,9 @@
         <v>25</v>
       </c>
     </row>
-    <row r="16" spans="1:19" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:19" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A16" s="15" t="s">
-        <v>7</v>
+        <v>49</v>
       </c>
       <c r="B16" s="4">
         <v>52137490</v>
@@ -2011,9 +2011,9 @@
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A17" s="15" t="s">
-        <v>8</v>
+        <v>50</v>
       </c>
       <c r="B17" s="4">
         <v>56286359</v>
@@ -2037,9 +2037,9 @@
         <v>25</v>
       </c>
     </row>
-    <row r="18" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A18" s="15" t="s">
-        <v>9</v>
+        <v>51</v>
       </c>
       <c r="B18" s="4">
         <v>102867490</v>
@@ -2063,9 +2063,9 @@
         <v>25</v>
       </c>
     </row>
-    <row r="19" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A19" s="15" t="s">
-        <v>10</v>
+        <v>52</v>
       </c>
       <c r="B19" s="4">
         <v>160146904</v>
@@ -2089,9 +2089,9 @@
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A20" s="15" t="s">
-        <v>11</v>
+        <v>53</v>
       </c>
       <c r="B20" s="4">
         <v>108511830</v>
@@ -2115,9 +2115,9 @@
         <v>25</v>
       </c>
     </row>
-    <row r="21" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A21" s="15" t="s">
-        <v>12</v>
+        <v>54</v>
       </c>
       <c r="B21" s="4">
         <v>135925706</v>
@@ -2141,9 +2141,9 @@
         <v>25</v>
       </c>
     </row>
-    <row r="22" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A22" s="15" t="s">
-        <v>13</v>
+        <v>55</v>
       </c>
       <c r="B22" s="4">
         <v>15264560.220579997</v>
@@ -2167,9 +2167,9 @@
         <v>30</v>
       </c>
     </row>
-    <row r="23" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A23" s="15" t="s">
-        <v>14</v>
+        <v>56</v>
       </c>
       <c r="B23" s="4">
         <v>275502951.37996</v>
@@ -2193,9 +2193,9 @@
         <v>30</v>
       </c>
     </row>
-    <row r="24" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A24" s="15" t="s">
-        <v>15</v>
+        <v>57</v>
       </c>
       <c r="B24" s="4">
         <v>197457275.13723999</v>
@@ -2219,9 +2219,9 @@
         <v>30</v>
       </c>
     </row>
-    <row r="25" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A25" s="15" t="s">
-        <v>16</v>
+        <v>58</v>
       </c>
       <c r="B25" s="4">
         <v>298093380.27333999</v>
@@ -2245,9 +2245,9 @@
         <v>30</v>
       </c>
     </row>
-    <row r="26" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A26" s="15" t="s">
-        <v>17</v>
+        <v>59</v>
       </c>
       <c r="B26" s="4">
         <v>28290780.670460004</v>
@@ -2271,9 +2271,9 @@
         <v>30</v>
       </c>
     </row>
-    <row r="27" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A27" s="15" t="s">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="B27" s="4">
         <v>437555960.32418001</v>
@@ -2297,9 +2297,9 @@
         <v>30</v>
       </c>
     </row>
-    <row r="28" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A28" s="15" t="s">
-        <v>19</v>
+        <v>61</v>
       </c>
       <c r="B28" s="4">
         <v>206223533.74474001</v>
@@ -2323,9 +2323,9 @@
         <v>30</v>
       </c>
     </row>
-    <row r="29" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A29" s="15" t="s">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="B29" s="4">
         <v>218127760.50577995</v>
@@ -2349,9 +2349,9 @@
         <v>30</v>
       </c>
     </row>
-    <row r="30" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A30" s="15" t="s">
-        <v>21</v>
+        <v>63</v>
       </c>
       <c r="B30" s="4">
         <v>23748126.856140003</v>
@@ -2375,9 +2375,9 @@
         <v>30</v>
       </c>
     </row>
-    <row r="31" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A31" s="15" t="s">
-        <v>22</v>
+        <v>64</v>
       </c>
       <c r="B31" s="4">
         <v>515154385.35320002</v>
@@ -2401,9 +2401,9 @@
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A32" s="15" t="s">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="B32" s="4">
         <v>321131564.82082009</v>
@@ -2427,9 +2427,9 @@
         <v>30</v>
       </c>
     </row>
-    <row r="33" spans="1:19" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:19" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A33" s="15" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="B33" s="4">
         <v>363838891.90964997</v>
@@ -2453,9 +2453,9 @@
         <v>30</v>
       </c>
     </row>
-    <row r="34" spans="1:19" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:19" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A34" s="15" t="s">
-        <v>25</v>
+        <v>67</v>
       </c>
       <c r="B34" s="12">
         <v>412322225.98115003</v>
@@ -2479,7 +2479,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
@@ -2497,7 +2497,7 @@
       <c r="R35" s="6"/>
       <c r="S35" s="6"/>
     </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
@@ -2515,7 +2515,7 @@
       <c r="R36" s="6"/>
       <c r="S36" s="6"/>
     </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
@@ -2533,7 +2533,7 @@
       <c r="R37" s="6"/>
       <c r="S37" s="6"/>
     </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
@@ -2551,7 +2551,7 @@
       <c r="R38" s="6"/>
       <c r="S38" s="6"/>
     </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
@@ -2563,7 +2563,7 @@
       <c r="L39" s="6"/>
       <c r="O39" s="6"/>
     </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
@@ -2575,397 +2575,397 @@
       <c r="L40" s="6"/>
       <c r="O40" s="6"/>
     </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:19" x14ac:dyDescent="0.3">
       <c r="L41" s="6"/>
       <c r="O41" s="6"/>
     </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:19" x14ac:dyDescent="0.3">
       <c r="L42" s="6"/>
       <c r="O42" s="6"/>
     </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:19" x14ac:dyDescent="0.3">
       <c r="L43" s="6"/>
       <c r="O43" s="6"/>
     </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:19" x14ac:dyDescent="0.3">
       <c r="L44" s="6"/>
       <c r="O44" s="6"/>
     </row>
-    <row r="45" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:19" x14ac:dyDescent="0.3">
       <c r="L45" s="6"/>
       <c r="O45" s="6"/>
     </row>
-    <row r="46" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:19" x14ac:dyDescent="0.3">
       <c r="L46" s="6"/>
       <c r="O46" s="6"/>
     </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:19" x14ac:dyDescent="0.3">
       <c r="L47" s="6"/>
       <c r="O47" s="6"/>
     </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:19" x14ac:dyDescent="0.3">
       <c r="L48" s="6"/>
       <c r="O48" s="6"/>
     </row>
-    <row r="49" spans="12:15" x14ac:dyDescent="0.25">
+    <row r="49" spans="12:15" x14ac:dyDescent="0.3">
       <c r="L49" s="6"/>
       <c r="O49" s="6"/>
     </row>
-    <row r="50" spans="12:15" x14ac:dyDescent="0.25">
+    <row r="50" spans="12:15" x14ac:dyDescent="0.3">
       <c r="L50" s="6"/>
       <c r="O50" s="6"/>
     </row>
-    <row r="51" spans="12:15" x14ac:dyDescent="0.25">
+    <row r="51" spans="12:15" x14ac:dyDescent="0.3">
       <c r="L51" s="6"/>
       <c r="O51" s="6"/>
     </row>
-    <row r="52" spans="12:15" x14ac:dyDescent="0.25">
+    <row r="52" spans="12:15" x14ac:dyDescent="0.3">
       <c r="L52" s="6"/>
       <c r="O52" s="6"/>
     </row>
-    <row r="53" spans="12:15" x14ac:dyDescent="0.25">
+    <row r="53" spans="12:15" x14ac:dyDescent="0.3">
       <c r="L53" s="6"/>
       <c r="O53" s="6"/>
     </row>
-    <row r="54" spans="12:15" x14ac:dyDescent="0.25">
+    <row r="54" spans="12:15" x14ac:dyDescent="0.3">
       <c r="L54" s="6"/>
       <c r="O54" s="6"/>
     </row>
-    <row r="55" spans="12:15" x14ac:dyDescent="0.25">
+    <row r="55" spans="12:15" x14ac:dyDescent="0.3">
       <c r="L55" s="6"/>
       <c r="O55" s="6"/>
     </row>
-    <row r="56" spans="12:15" x14ac:dyDescent="0.25">
+    <row r="56" spans="12:15" x14ac:dyDescent="0.3">
       <c r="L56" s="6"/>
       <c r="O56" s="6"/>
     </row>
-    <row r="57" spans="12:15" x14ac:dyDescent="0.25">
+    <row r="57" spans="12:15" x14ac:dyDescent="0.3">
       <c r="L57" s="6"/>
       <c r="O57" s="6"/>
     </row>
-    <row r="58" spans="12:15" x14ac:dyDescent="0.25">
+    <row r="58" spans="12:15" x14ac:dyDescent="0.3">
       <c r="L58" s="6"/>
       <c r="O58" s="6"/>
     </row>
-    <row r="59" spans="12:15" x14ac:dyDescent="0.25">
+    <row r="59" spans="12:15" x14ac:dyDescent="0.3">
       <c r="L59" s="6"/>
       <c r="O59" s="6"/>
     </row>
-    <row r="60" spans="12:15" x14ac:dyDescent="0.25">
+    <row r="60" spans="12:15" x14ac:dyDescent="0.3">
       <c r="L60" s="6"/>
       <c r="O60" s="6"/>
     </row>
-    <row r="61" spans="12:15" x14ac:dyDescent="0.25">
+    <row r="61" spans="12:15" x14ac:dyDescent="0.3">
       <c r="L61" s="6"/>
       <c r="O61" s="6"/>
     </row>
-    <row r="62" spans="12:15" x14ac:dyDescent="0.25">
+    <row r="62" spans="12:15" x14ac:dyDescent="0.3">
       <c r="L62" s="6"/>
       <c r="O62" s="6"/>
     </row>
-    <row r="63" spans="12:15" x14ac:dyDescent="0.25">
+    <row r="63" spans="12:15" x14ac:dyDescent="0.3">
       <c r="L63" s="6"/>
       <c r="O63" s="6"/>
     </row>
-    <row r="64" spans="12:15" x14ac:dyDescent="0.25">
+    <row r="64" spans="12:15" x14ac:dyDescent="0.3">
       <c r="L64" s="6"/>
       <c r="O64" s="6"/>
     </row>
-    <row r="65" spans="12:15" x14ac:dyDescent="0.25">
+    <row r="65" spans="12:15" x14ac:dyDescent="0.3">
       <c r="L65" s="6"/>
       <c r="O65" s="6"/>
     </row>
-    <row r="66" spans="12:15" x14ac:dyDescent="0.25">
+    <row r="66" spans="12:15" x14ac:dyDescent="0.3">
       <c r="L66" s="6"/>
       <c r="O66" s="6"/>
     </row>
-    <row r="67" spans="12:15" x14ac:dyDescent="0.25">
+    <row r="67" spans="12:15" x14ac:dyDescent="0.3">
       <c r="L67" s="6"/>
       <c r="O67" s="6"/>
     </row>
-    <row r="68" spans="12:15" x14ac:dyDescent="0.25">
+    <row r="68" spans="12:15" x14ac:dyDescent="0.3">
       <c r="L68" s="6"/>
       <c r="O68" s="6"/>
     </row>
-    <row r="69" spans="12:15" x14ac:dyDescent="0.25">
+    <row r="69" spans="12:15" x14ac:dyDescent="0.3">
       <c r="L69" s="6"/>
       <c r="O69" s="6"/>
     </row>
-    <row r="70" spans="12:15" x14ac:dyDescent="0.25">
+    <row r="70" spans="12:15" x14ac:dyDescent="0.3">
       <c r="L70" s="6"/>
       <c r="O70" s="6"/>
     </row>
-    <row r="71" spans="12:15" x14ac:dyDescent="0.25">
+    <row r="71" spans="12:15" x14ac:dyDescent="0.3">
       <c r="L71" s="6"/>
       <c r="O71" s="6"/>
     </row>
-    <row r="72" spans="12:15" x14ac:dyDescent="0.25">
+    <row r="72" spans="12:15" x14ac:dyDescent="0.3">
       <c r="L72" s="6"/>
       <c r="O72" s="6"/>
     </row>
-    <row r="73" spans="12:15" x14ac:dyDescent="0.25">
+    <row r="73" spans="12:15" x14ac:dyDescent="0.3">
       <c r="L73" s="6"/>
       <c r="O73" s="6"/>
     </row>
-    <row r="74" spans="12:15" x14ac:dyDescent="0.25">
+    <row r="74" spans="12:15" x14ac:dyDescent="0.3">
       <c r="L74" s="6"/>
       <c r="O74" s="6"/>
     </row>
-    <row r="75" spans="12:15" x14ac:dyDescent="0.25">
+    <row r="75" spans="12:15" x14ac:dyDescent="0.3">
       <c r="L75" s="6"/>
       <c r="O75" s="6"/>
     </row>
-    <row r="76" spans="12:15" x14ac:dyDescent="0.25">
+    <row r="76" spans="12:15" x14ac:dyDescent="0.3">
       <c r="L76" s="6"/>
       <c r="O76" s="6"/>
     </row>
-    <row r="77" spans="12:15" x14ac:dyDescent="0.25">
+    <row r="77" spans="12:15" x14ac:dyDescent="0.3">
       <c r="L77" s="6"/>
       <c r="O77" s="6"/>
     </row>
-    <row r="78" spans="12:15" x14ac:dyDescent="0.25">
+    <row r="78" spans="12:15" x14ac:dyDescent="0.3">
       <c r="L78" s="6"/>
       <c r="O78" s="6"/>
     </row>
-    <row r="79" spans="12:15" x14ac:dyDescent="0.25">
+    <row r="79" spans="12:15" x14ac:dyDescent="0.3">
       <c r="L79" s="6"/>
       <c r="O79" s="6"/>
     </row>
-    <row r="80" spans="12:15" x14ac:dyDescent="0.25">
+    <row r="80" spans="12:15" x14ac:dyDescent="0.3">
       <c r="L80" s="6"/>
       <c r="O80" s="6"/>
     </row>
-    <row r="81" spans="12:15" x14ac:dyDescent="0.25">
+    <row r="81" spans="12:15" x14ac:dyDescent="0.3">
       <c r="L81" s="6"/>
       <c r="O81" s="6"/>
     </row>
-    <row r="82" spans="12:15" x14ac:dyDescent="0.25">
+    <row r="82" spans="12:15" x14ac:dyDescent="0.3">
       <c r="L82" s="6"/>
       <c r="O82" s="6"/>
     </row>
-    <row r="83" spans="12:15" x14ac:dyDescent="0.25">
+    <row r="83" spans="12:15" x14ac:dyDescent="0.3">
       <c r="L83" s="6"/>
       <c r="O83" s="6"/>
     </row>
-    <row r="84" spans="12:15" x14ac:dyDescent="0.25">
+    <row r="84" spans="12:15" x14ac:dyDescent="0.3">
       <c r="L84" s="6"/>
       <c r="O84" s="6"/>
     </row>
-    <row r="85" spans="12:15" x14ac:dyDescent="0.25">
+    <row r="85" spans="12:15" x14ac:dyDescent="0.3">
       <c r="L85" s="6"/>
       <c r="O85" s="6"/>
     </row>
-    <row r="86" spans="12:15" x14ac:dyDescent="0.25">
+    <row r="86" spans="12:15" x14ac:dyDescent="0.3">
       <c r="L86" s="6"/>
       <c r="O86" s="6"/>
     </row>
-    <row r="87" spans="12:15" x14ac:dyDescent="0.25">
+    <row r="87" spans="12:15" x14ac:dyDescent="0.3">
       <c r="L87" s="6"/>
       <c r="O87" s="6"/>
     </row>
-    <row r="88" spans="12:15" x14ac:dyDescent="0.25">
+    <row r="88" spans="12:15" x14ac:dyDescent="0.3">
       <c r="L88" s="6"/>
       <c r="O88" s="6"/>
     </row>
-    <row r="89" spans="12:15" x14ac:dyDescent="0.25">
+    <row r="89" spans="12:15" x14ac:dyDescent="0.3">
       <c r="L89" s="6"/>
       <c r="O89" s="6"/>
     </row>
-    <row r="90" spans="12:15" x14ac:dyDescent="0.25">
+    <row r="90" spans="12:15" x14ac:dyDescent="0.3">
       <c r="L90" s="6"/>
       <c r="O90" s="6"/>
     </row>
-    <row r="91" spans="12:15" x14ac:dyDescent="0.25">
+    <row r="91" spans="12:15" x14ac:dyDescent="0.3">
       <c r="L91" s="6"/>
       <c r="O91" s="6"/>
     </row>
-    <row r="92" spans="12:15" x14ac:dyDescent="0.25">
+    <row r="92" spans="12:15" x14ac:dyDescent="0.3">
       <c r="L92" s="6"/>
       <c r="O92" s="6"/>
     </row>
-    <row r="93" spans="12:15" x14ac:dyDescent="0.25">
+    <row r="93" spans="12:15" x14ac:dyDescent="0.3">
       <c r="L93" s="6"/>
       <c r="O93" s="6"/>
     </row>
-    <row r="94" spans="12:15" x14ac:dyDescent="0.25">
+    <row r="94" spans="12:15" x14ac:dyDescent="0.3">
       <c r="L94" s="6"/>
       <c r="O94" s="6"/>
     </row>
-    <row r="95" spans="12:15" x14ac:dyDescent="0.25">
+    <row r="95" spans="12:15" x14ac:dyDescent="0.3">
       <c r="L95" s="6"/>
       <c r="O95" s="6"/>
     </row>
-    <row r="96" spans="12:15" x14ac:dyDescent="0.25">
+    <row r="96" spans="12:15" x14ac:dyDescent="0.3">
       <c r="L96" s="6"/>
       <c r="O96" s="6"/>
     </row>
-    <row r="97" spans="12:15" x14ac:dyDescent="0.25">
+    <row r="97" spans="12:15" x14ac:dyDescent="0.3">
       <c r="L97" s="6"/>
       <c r="O97" s="6"/>
     </row>
-    <row r="98" spans="12:15" x14ac:dyDescent="0.25">
+    <row r="98" spans="12:15" x14ac:dyDescent="0.3">
       <c r="L98" s="6"/>
       <c r="O98" s="6"/>
     </row>
-    <row r="99" spans="12:15" x14ac:dyDescent="0.25">
+    <row r="99" spans="12:15" x14ac:dyDescent="0.3">
       <c r="L99" s="6"/>
       <c r="O99" s="6"/>
     </row>
-    <row r="100" spans="12:15" x14ac:dyDescent="0.25">
+    <row r="100" spans="12:15" x14ac:dyDescent="0.3">
       <c r="L100" s="6"/>
       <c r="O100" s="6"/>
     </row>
-    <row r="101" spans="12:15" x14ac:dyDescent="0.25">
+    <row r="101" spans="12:15" x14ac:dyDescent="0.3">
       <c r="L101" s="6"/>
       <c r="O101" s="6"/>
     </row>
-    <row r="102" spans="12:15" x14ac:dyDescent="0.25">
+    <row r="102" spans="12:15" x14ac:dyDescent="0.3">
       <c r="L102" s="6"/>
       <c r="O102" s="6"/>
     </row>
-    <row r="103" spans="12:15" x14ac:dyDescent="0.25">
+    <row r="103" spans="12:15" x14ac:dyDescent="0.3">
       <c r="L103" s="6"/>
       <c r="O103" s="6"/>
     </row>
-    <row r="104" spans="12:15" x14ac:dyDescent="0.25">
+    <row r="104" spans="12:15" x14ac:dyDescent="0.3">
       <c r="L104" s="6"/>
       <c r="O104" s="6"/>
     </row>
-    <row r="105" spans="12:15" x14ac:dyDescent="0.25">
+    <row r="105" spans="12:15" x14ac:dyDescent="0.3">
       <c r="L105" s="6"/>
       <c r="O105" s="6"/>
     </row>
-    <row r="106" spans="12:15" x14ac:dyDescent="0.25">
+    <row r="106" spans="12:15" x14ac:dyDescent="0.3">
       <c r="L106" s="6"/>
       <c r="O106" s="6"/>
     </row>
-    <row r="107" spans="12:15" x14ac:dyDescent="0.25">
+    <row r="107" spans="12:15" x14ac:dyDescent="0.3">
       <c r="L107" s="6"/>
       <c r="O107" s="6"/>
     </row>
-    <row r="108" spans="12:15" x14ac:dyDescent="0.25">
+    <row r="108" spans="12:15" x14ac:dyDescent="0.3">
       <c r="L108" s="6"/>
       <c r="O108" s="6"/>
     </row>
-    <row r="109" spans="12:15" x14ac:dyDescent="0.25">
+    <row r="109" spans="12:15" x14ac:dyDescent="0.3">
       <c r="L109" s="6"/>
       <c r="O109" s="6"/>
     </row>
-    <row r="110" spans="12:15" x14ac:dyDescent="0.25">
+    <row r="110" spans="12:15" x14ac:dyDescent="0.3">
       <c r="L110" s="6"/>
       <c r="O110" s="6"/>
     </row>
-    <row r="111" spans="12:15" x14ac:dyDescent="0.25">
+    <row r="111" spans="12:15" x14ac:dyDescent="0.3">
       <c r="L111" s="6"/>
       <c r="O111" s="6"/>
     </row>
-    <row r="112" spans="12:15" x14ac:dyDescent="0.25">
+    <row r="112" spans="12:15" x14ac:dyDescent="0.3">
       <c r="L112" s="6"/>
       <c r="O112" s="6"/>
     </row>
-    <row r="113" spans="12:15" x14ac:dyDescent="0.25">
+    <row r="113" spans="12:15" x14ac:dyDescent="0.3">
       <c r="L113" s="6"/>
       <c r="O113" s="6"/>
     </row>
-    <row r="114" spans="12:15" x14ac:dyDescent="0.25">
+    <row r="114" spans="12:15" x14ac:dyDescent="0.3">
       <c r="L114" s="6"/>
       <c r="O114" s="6"/>
     </row>
-    <row r="115" spans="12:15" x14ac:dyDescent="0.25">
+    <row r="115" spans="12:15" x14ac:dyDescent="0.3">
       <c r="L115" s="6"/>
       <c r="O115" s="6"/>
     </row>
-    <row r="116" spans="12:15" x14ac:dyDescent="0.25">
+    <row r="116" spans="12:15" x14ac:dyDescent="0.3">
       <c r="L116" s="6"/>
       <c r="O116" s="6"/>
     </row>
-    <row r="117" spans="12:15" x14ac:dyDescent="0.25">
+    <row r="117" spans="12:15" x14ac:dyDescent="0.3">
       <c r="L117" s="6"/>
       <c r="O117" s="6"/>
     </row>
-    <row r="118" spans="12:15" x14ac:dyDescent="0.25">
+    <row r="118" spans="12:15" x14ac:dyDescent="0.3">
       <c r="L118" s="6"/>
       <c r="O118" s="6"/>
     </row>
-    <row r="119" spans="12:15" x14ac:dyDescent="0.25">
+    <row r="119" spans="12:15" x14ac:dyDescent="0.3">
       <c r="L119" s="6"/>
       <c r="O119" s="6"/>
     </row>
-    <row r="120" spans="12:15" x14ac:dyDescent="0.25">
+    <row r="120" spans="12:15" x14ac:dyDescent="0.3">
       <c r="L120" s="6"/>
       <c r="O120" s="6"/>
     </row>
-    <row r="121" spans="12:15" x14ac:dyDescent="0.25">
+    <row r="121" spans="12:15" x14ac:dyDescent="0.3">
       <c r="L121" s="6"/>
       <c r="O121" s="6"/>
     </row>
-    <row r="122" spans="12:15" x14ac:dyDescent="0.25">
+    <row r="122" spans="12:15" x14ac:dyDescent="0.3">
       <c r="L122" s="6"/>
       <c r="O122" s="6"/>
     </row>
-    <row r="123" spans="12:15" x14ac:dyDescent="0.25">
+    <row r="123" spans="12:15" x14ac:dyDescent="0.3">
       <c r="L123" s="6"/>
       <c r="O123" s="6"/>
     </row>
-    <row r="124" spans="12:15" x14ac:dyDescent="0.25">
+    <row r="124" spans="12:15" x14ac:dyDescent="0.3">
       <c r="L124" s="6"/>
       <c r="O124" s="6"/>
     </row>
-    <row r="125" spans="12:15" x14ac:dyDescent="0.25">
+    <row r="125" spans="12:15" x14ac:dyDescent="0.3">
       <c r="L125" s="6"/>
       <c r="O125" s="6"/>
     </row>
-    <row r="126" spans="12:15" x14ac:dyDescent="0.25">
+    <row r="126" spans="12:15" x14ac:dyDescent="0.3">
       <c r="L126" s="6"/>
       <c r="O126" s="6"/>
     </row>
-    <row r="127" spans="12:15" x14ac:dyDescent="0.25">
+    <row r="127" spans="12:15" x14ac:dyDescent="0.3">
       <c r="L127" s="6"/>
       <c r="O127" s="6"/>
     </row>
-    <row r="128" spans="12:15" x14ac:dyDescent="0.25">
+    <row r="128" spans="12:15" x14ac:dyDescent="0.3">
       <c r="L128" s="6"/>
       <c r="O128" s="6"/>
     </row>
-    <row r="129" spans="12:15" x14ac:dyDescent="0.25">
+    <row r="129" spans="12:15" x14ac:dyDescent="0.3">
       <c r="L129" s="6"/>
       <c r="O129" s="6"/>
     </row>
-    <row r="130" spans="12:15" x14ac:dyDescent="0.25">
+    <row r="130" spans="12:15" x14ac:dyDescent="0.3">
       <c r="L130" s="6"/>
       <c r="O130" s="6"/>
     </row>
-    <row r="131" spans="12:15" x14ac:dyDescent="0.25">
+    <row r="131" spans="12:15" x14ac:dyDescent="0.3">
       <c r="L131" s="6"/>
     </row>
-    <row r="132" spans="12:15" x14ac:dyDescent="0.25">
+    <row r="132" spans="12:15" x14ac:dyDescent="0.3">
       <c r="L132" s="6"/>
     </row>
-    <row r="133" spans="12:15" x14ac:dyDescent="0.25">
+    <row r="133" spans="12:15" x14ac:dyDescent="0.3">
       <c r="L133" s="6"/>
     </row>
-    <row r="134" spans="12:15" x14ac:dyDescent="0.25">
+    <row r="134" spans="12:15" x14ac:dyDescent="0.3">
       <c r="L134" s="6"/>
     </row>
-    <row r="135" spans="12:15" x14ac:dyDescent="0.25">
+    <row r="135" spans="12:15" x14ac:dyDescent="0.3">
       <c r="L135" s="6"/>
     </row>
-    <row r="136" spans="12:15" x14ac:dyDescent="0.25">
+    <row r="136" spans="12:15" x14ac:dyDescent="0.3">
       <c r="L136" s="6"/>
     </row>
-    <row r="137" spans="12:15" x14ac:dyDescent="0.25">
+    <row r="137" spans="12:15" x14ac:dyDescent="0.3">
       <c r="L137" s="6"/>
     </row>
-    <row r="138" spans="12:15" x14ac:dyDescent="0.25">
+    <row r="138" spans="12:15" x14ac:dyDescent="0.3">
       <c r="L138" s="6"/>
     </row>
-    <row r="139" spans="12:15" x14ac:dyDescent="0.25">
+    <row r="139" spans="12:15" x14ac:dyDescent="0.3">
       <c r="L139" s="6"/>
     </row>
-    <row r="140" spans="12:15" x14ac:dyDescent="0.25">
+    <row r="140" spans="12:15" x14ac:dyDescent="0.3">
       <c r="L140" s="6"/>
     </row>
-    <row r="141" spans="12:15" x14ac:dyDescent="0.25">
+    <row r="141" spans="12:15" x14ac:dyDescent="0.3">
       <c r="L141" s="6"/>
     </row>
   </sheetData>
@@ -2979,30 +2979,30 @@
     <tabColor rgb="FFFFC000"/>
   </sheetPr>
   <dimension ref="A1:E77"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="5" width="20.42578125" customWidth="1"/>
-    <col min="6" max="6" width="16.7109375" customWidth="1"/>
+    <col min="2" max="5" width="20.44140625" customWidth="1"/>
+    <col min="6" max="6" width="16.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="18" t="s">
-        <v>47</v>
+        <v>14</v>
       </c>
       <c r="C1" s="18" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="D1" s="18" t="s">
-        <v>65</v>
+        <v>32</v>
       </c>
       <c r="E1" s="18" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>43831</v>
       </c>
@@ -3019,7 +3019,7 @@
         <v>10.719228759073401</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>43862</v>
       </c>
@@ -3036,7 +3036,7 @@
         <v>11.8156578602217</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>43891</v>
       </c>
@@ -3053,7 +3053,7 @@
         <v>10.2433876763639</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>43922</v>
       </c>
@@ -3070,7 +3070,7 @@
         <v>10.340269746430501</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>43952</v>
       </c>
@@ -3087,7 +3087,7 @@
         <v>10.312548639404501</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>43983</v>
       </c>
@@ -3104,7 +3104,7 @@
         <v>18.2336243574108</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>44013</v>
       </c>
@@ -3121,7 +3121,7 @@
         <v>13.8691146016592</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>44044</v>
       </c>
@@ -3138,7 +3138,7 @@
         <v>12.944197094807899</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>44075</v>
       </c>
@@ -3155,7 +3155,7 @@
         <v>12.5176320976511</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>44105</v>
       </c>
@@ -3172,7 +3172,7 @@
         <v>12.3896297806891</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>44136</v>
       </c>
@@ -3189,7 +3189,7 @@
         <v>12.5874755166606</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>44166</v>
       </c>
@@ -3206,7 +3206,7 @@
         <v>12.5940777059503</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>44197</v>
       </c>
@@ -3223,7 +3223,7 @@
         <v>12.379576440019187</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>44228</v>
       </c>
@@ -3240,7 +3240,7 @@
         <v>12.377715198360177</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>44256</v>
       </c>
@@ -3257,7 +3257,7 @@
         <v>11.361400576983991</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>44287</v>
       </c>
@@ -3274,7 +3274,7 @@
         <v>11.372523867780233</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>44317</v>
       </c>
@@ -3291,7 +3291,7 @@
         <v>10.746110004903418</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>44348</v>
       </c>
@@ -3308,7 +3308,7 @@
         <v>11.562102167016562</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>44378</v>
       </c>
@@ -3325,7 +3325,7 @@
         <v>10.977702133669275</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>44409</v>
       </c>
@@ -3342,7 +3342,7 @@
         <v>11.774460587659025</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>44440</v>
       </c>
@@ -3359,7 +3359,7 @@
         <v>11.141346571892901</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>44470</v>
       </c>
@@ -3376,7 +3376,7 @@
         <v>11.200032768122774</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>44501</v>
       </c>
@@ -3393,7 +3393,7 @@
         <v>10.528120471773271</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>44531</v>
       </c>
@@ -3410,7 +3410,7 @@
         <v>10.225852688070475</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>44562</v>
       </c>
@@ -3427,7 +3427,7 @@
         <v>10.55972676220901</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>44593</v>
       </c>
@@ -3444,7 +3444,7 @@
         <v>12.765414017146609</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>44621</v>
       </c>
@@ -3461,7 +3461,7 @@
         <v>12.578325122960734</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>44652</v>
       </c>
@@ -3478,7 +3478,7 @@
         <v>12.117522056786557</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>44682</v>
       </c>
@@ -3495,7 +3495,7 @@
         <v>12.026099626046072</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>44713</v>
       </c>
@@ -3512,7 +3512,7 @@
         <v>12.31460008102899</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>44743</v>
       </c>
@@ -3529,7 +3529,7 @@
         <v>11.847569395979839</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>44774</v>
       </c>
@@ -3546,7 +3546,7 @@
         <v>12.712760451336536</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>44805</v>
       </c>
@@ -3563,7 +3563,7 @@
         <v>12.166085370101881</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <v>44835</v>
       </c>
@@ -3580,7 +3580,7 @@
         <v>12.703783314642594</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <v>44866</v>
       </c>
@@ -3597,7 +3597,7 @@
         <v>12.871356148448539</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <v>44896</v>
       </c>
@@ -3614,7 +3614,7 @@
         <v>14.118804053632847</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <v>44927</v>
       </c>
@@ -3631,7 +3631,7 @@
         <v>11.993579851779955</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <v>44958</v>
       </c>
@@ -3648,7 +3648,7 @@
         <v>12.922698771861038</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <v>44986</v>
       </c>
@@ -3665,7 +3665,7 @@
         <v>12.97354685641468</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
         <v>45017</v>
       </c>
@@ -3682,7 +3682,7 @@
         <v>12.67808615095268</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
         <v>45047</v>
       </c>
@@ -3699,7 +3699,7 @@
         <v>12.442470024549779</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
         <v>45078</v>
       </c>
@@ -3716,7 +3716,7 @@
         <v>13.672523164479555</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
         <v>45108</v>
       </c>
@@ -3733,7 +3733,7 @@
         <v>14.949607688077657</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" s="1">
         <v>45139</v>
       </c>
@@ -3750,7 +3750,7 @@
         <v>15.043324210674191</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
         <v>45170</v>
       </c>
@@ -3767,7 +3767,7 @@
         <v>15.218753878942657</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
         <v>45200</v>
       </c>
@@ -3784,7 +3784,7 @@
         <v>15.350072263951747</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
         <v>45231</v>
       </c>
@@ -3801,7 +3801,7 @@
         <v>14.754266996100544</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" s="1">
         <v>45261</v>
       </c>
@@ -3818,7 +3818,7 @@
         <v>14.990001681649373</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50" s="1">
         <v>45292</v>
       </c>
@@ -3835,7 +3835,7 @@
         <v>14.38408780807123</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51" s="1">
         <v>45323</v>
       </c>
@@ -3852,7 +3852,7 @@
         <v>14.141570703260992</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52" s="1">
         <v>45352</v>
       </c>
@@ -3869,7 +3869,7 @@
         <v>14.049079836824669</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53" s="1">
         <v>45383</v>
       </c>
@@ -3886,7 +3886,7 @@
         <v>14.242356267334255</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54" s="1">
         <v>45413</v>
       </c>
@@ -3903,7 +3903,7 @@
         <v>14.018579560869021</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55" s="1">
         <v>45444</v>
       </c>
@@ -3920,7 +3920,7 @@
         <v>14.207132785821647</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56" s="1">
         <v>45474</v>
       </c>
@@ -3937,7 +3937,7 @@
         <v>14.659792731778087</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57" s="1">
         <v>45505</v>
       </c>
@@ -3954,7 +3954,7 @@
         <v>14.271121303912093</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58" s="1">
         <v>45536</v>
       </c>
@@ -3971,7 +3971,7 @@
         <v>14.197514996616409</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A59" s="1">
         <v>45566</v>
       </c>
@@ -3988,7 +3988,7 @@
         <v>14.253898291514069</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60" s="1">
         <v>45597</v>
       </c>
@@ -4005,7 +4005,7 @@
         <v>13.830644721498263</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61" s="1">
         <v>45627</v>
       </c>
@@ -4022,7 +4022,7 @@
         <v>14.294600880549577</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62" s="1">
         <v>45658</v>
       </c>
@@ -4039,7 +4039,7 @@
         <v>14.170136503688898</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63" s="1">
         <v>45689</v>
       </c>
@@ -4056,7 +4056,7 @@
         <v>13.840248348263504</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64" s="1">
         <v>45717</v>
       </c>
@@ -4073,7 +4073,7 @@
         <v>14.070991192061861</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65" s="1">
         <v>45748</v>
       </c>
@@ -4090,7 +4090,7 @@
         <v>14.115056212942227</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A66" s="1">
         <v>45778</v>
       </c>
@@ -4107,7 +4107,7 @@
         <v>13.961753599170779</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A67" s="1">
         <v>45809</v>
       </c>
@@ -4124,7 +4124,7 @@
         <v>14.663488225326326</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A68" s="1">
         <v>45839</v>
       </c>
@@ -4141,7 +4141,7 @@
         <v>14.406120400092496</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A69" s="1">
         <v>45870</v>
       </c>
@@ -4158,7 +4158,7 @@
         <v>15.360281958435532</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A70" s="1">
         <v>45901</v>
       </c>
@@ -4175,7 +4175,7 @@
         <v>15.31515427610011</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A71" s="1">
         <v>45931</v>
       </c>
@@ -4192,7 +4192,7 @@
         <v>14.69079869392314</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A72" s="1">
         <v>45962</v>
       </c>
@@ -4209,7 +4209,7 @@
         <v>14.388144152077107</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73" s="1">
         <v>45992</v>
       </c>
@@ -4226,7 +4226,7 @@
         <v>14.921944414934829</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A74" s="1">
         <v>46023</v>
       </c>
@@ -4243,7 +4243,7 @@
         <v>13.496913442952929</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A75" s="1">
         <v>46054</v>
       </c>
@@ -4260,7 +4260,7 @@
         <v>14.285709376622865</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76" s="1">
         <v>46082</v>
       </c>
@@ -4277,7 +4277,7 @@
         <v>15.239438433363198</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A77" s="1">
         <v>46113</v>
       </c>
@@ -4305,36 +4305,36 @@
     <tabColor rgb="FFFFC000"/>
   </sheetPr>
   <dimension ref="A1:U77"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="22" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21.42578125" customWidth="1"/>
-    <col min="6" max="6" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.44140625" customWidth="1"/>
+    <col min="6" max="6" width="19.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:21" ht="44.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="18" t="s">
-        <v>52</v>
+        <v>19</v>
       </c>
       <c r="C1" s="18" t="s">
-        <v>66</v>
+        <v>33</v>
       </c>
       <c r="D1" s="18" t="s">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="E1" s="18" t="s">
-        <v>67</v>
+        <v>34</v>
       </c>
       <c r="F1" s="17" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>43831</v>
       </c>
@@ -4366,7 +4366,7 @@
       <c r="T2" s="6"/>
       <c r="U2" s="6"/>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>43862</v>
       </c>
@@ -4398,7 +4398,7 @@
       <c r="T3" s="6"/>
       <c r="U3" s="6"/>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>43891</v>
       </c>
@@ -4430,7 +4430,7 @@
       <c r="T4" s="6"/>
       <c r="U4" s="6"/>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>43922</v>
       </c>
@@ -4462,7 +4462,7 @@
       <c r="T5" s="6"/>
       <c r="U5" s="6"/>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>43952</v>
       </c>
@@ -4494,7 +4494,7 @@
       <c r="T6" s="6"/>
       <c r="U6" s="6"/>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>43983</v>
       </c>
@@ -4526,7 +4526,7 @@
       <c r="T7" s="6"/>
       <c r="U7" s="6"/>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>44013</v>
       </c>
@@ -4558,7 +4558,7 @@
       <c r="T8" s="6"/>
       <c r="U8" s="6"/>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>44044</v>
       </c>
@@ -4578,7 +4578,7 @@
         <v>23181.914000000001</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>44075</v>
       </c>
@@ -4598,7 +4598,7 @@
         <v>20149.131000000001</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>44105</v>
       </c>
@@ -4618,7 +4618,7 @@
         <v>21440.789000000001</v>
       </c>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>44136</v>
       </c>
@@ -4638,7 +4638,7 @@
         <v>21160.582999999999</v>
       </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>44166</v>
       </c>
@@ -4658,7 +4658,7 @@
         <v>21845.452999999998</v>
       </c>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>44197</v>
       </c>
@@ -4678,7 +4678,7 @@
         <v>16107.406999999999</v>
       </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>44228</v>
       </c>
@@ -4698,7 +4698,7 @@
         <v>14030.112000000001</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>44256</v>
       </c>
@@ -4718,7 +4718,7 @@
         <v>17843.615999999995</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>44287</v>
       </c>
@@ -4738,7 +4738,7 @@
         <v>16225.648000000001</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>44317</v>
       </c>
@@ -4758,7 +4758,7 @@
         <v>13131.108</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>44348</v>
       </c>
@@ -4778,7 +4778,7 @@
         <v>18224.972000000002</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>44378</v>
       </c>
@@ -4798,7 +4798,7 @@
         <v>18619.845000000001</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>44409</v>
       </c>
@@ -4818,7 +4818,7 @@
         <v>18348.053999999996</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>44440</v>
       </c>
@@ -4838,7 +4838,7 @@
         <v>18343.766000000003</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>44470</v>
       </c>
@@ -4858,7 +4858,7 @@
         <v>16549.139000000003</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>44501</v>
       </c>
@@ -4878,7 +4878,7 @@
         <v>17997.911</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>44531</v>
       </c>
@@ -4898,7 +4898,7 @@
         <v>19970.819</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>44562</v>
       </c>
@@ -4918,7 +4918,7 @@
         <v>22202.407999999999</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>44593</v>
       </c>
@@ -4938,7 +4938,7 @@
         <v>18854.906999999999</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>44621</v>
       </c>
@@ -4958,7 +4958,7 @@
         <v>24777.637999999995</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>44652</v>
       </c>
@@ -4978,7 +4978,7 @@
         <v>30016.632999999998</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>44682</v>
       </c>
@@ -4998,7 +4998,7 @@
         <v>30617.290999999997</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>44713</v>
       </c>
@@ -5018,7 +5018,7 @@
         <v>38907.341999999997</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>44743</v>
       </c>
@@ -5038,7 +5038,7 @@
         <v>36296.294000000002</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>44774</v>
       </c>
@@ -5058,7 +5058,7 @@
         <v>39351.341999999997</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>44805</v>
       </c>
@@ -5078,7 +5078,7 @@
         <v>37776.210999999996</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <v>44835</v>
       </c>
@@ -5098,7 +5098,7 @@
         <v>42309.145999999993</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <v>44866</v>
       </c>
@@ -5118,7 +5118,7 @@
         <v>46197.886000000006</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <v>44896</v>
       </c>
@@ -5138,7 +5138,7 @@
         <v>52484.076554779982</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <v>44927</v>
       </c>
@@ -5158,7 +5158,7 @@
         <v>44788.414999999994</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <v>44958</v>
       </c>
@@ -5178,7 +5178,7 @@
         <v>42709.222999999998</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <v>44986</v>
       </c>
@@ -5198,7 +5198,7 @@
         <v>47776.941999999995</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
         <v>45017</v>
       </c>
@@ -5218,7 +5218,7 @@
         <v>53607.633999999998</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
         <v>45047</v>
       </c>
@@ -5238,7 +5238,7 @@
         <v>62441.786000000007</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
         <v>45078</v>
       </c>
@@ -5258,7 +5258,7 @@
         <v>73743.990999999995</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
         <v>45108</v>
       </c>
@@ -5278,7 +5278,7 @@
         <v>83578.316999999995</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" s="1">
         <v>45139</v>
       </c>
@@ -5298,7 +5298,7 @@
         <v>104099.531</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
         <v>45170</v>
       </c>
@@ -5318,7 +5318,7 @@
         <v>98769.524999999994</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
         <v>45200</v>
       </c>
@@ -5338,7 +5338,7 @@
         <v>97434.119000000006</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
         <v>45231</v>
       </c>
@@ -5358,7 +5358,7 @@
         <v>102597.833</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" s="1">
         <v>45261</v>
       </c>
@@ -5378,7 +5378,7 @@
         <v>116650.118</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" s="1">
         <v>45292</v>
       </c>
@@ -5398,7 +5398,7 @@
         <v>97707.150078009989</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" s="1">
         <v>45323</v>
       </c>
@@ -5418,7 +5418,7 @@
         <v>88849.94849142</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" s="1">
         <v>45352</v>
       </c>
@@ -5438,7 +5438,7 @@
         <v>96595.64313887</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" s="1">
         <v>45383</v>
       </c>
@@ -5458,7 +5458,7 @@
         <v>97575.352863500011</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54" s="1">
         <v>45413</v>
       </c>
@@ -5478,7 +5478,7 @@
         <v>116327.13732456003</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55" s="1">
         <v>45444</v>
       </c>
@@ -5498,7 +5498,7 @@
         <v>111671.26103940998</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56" s="1">
         <v>45474</v>
       </c>
@@ -5518,7 +5518,7 @@
         <v>134788.26277259999</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57" s="1">
         <v>45505</v>
       </c>
@@ -5538,7 +5538,7 @@
         <v>128202.74347917004</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58" s="1">
         <v>45536</v>
       </c>
@@ -5558,7 +5558,7 @@
         <v>127117.53499018993</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59" s="1">
         <v>45566</v>
       </c>
@@ -5578,7 +5578,7 @@
         <v>138999.90930607004</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60" s="1">
         <v>45597</v>
       </c>
@@ -5598,7 +5598,7 @@
         <v>140548.92577937001</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61" s="1">
         <v>45627</v>
       </c>
@@ -5618,7 +5618,7 @@
         <v>172876.58343932993</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62" s="1">
         <v>45658</v>
       </c>
@@ -5638,7 +5638,7 @@
         <v>135058.70185327003</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63" s="1">
         <v>45689</v>
       </c>
@@ -5658,7 +5658,7 @@
         <v>125976.87312116</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64" s="1">
         <v>45717</v>
       </c>
@@ -5678,7 +5678,7 @@
         <v>132558.23825878999</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A65" s="1">
         <v>45748</v>
       </c>
@@ -5698,7 +5698,7 @@
         <v>141810.74802571</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A66" s="1">
         <v>45778</v>
       </c>
@@ -5718,7 +5718,7 @@
         <v>143604.04393760997</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A67" s="1">
         <v>45809</v>
       </c>
@@ -5738,7 +5738,7 @@
         <v>163851.34982965991</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A68" s="1">
         <v>45839</v>
       </c>
@@ -5758,7 +5758,7 @@
         <v>181452.7779534201</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A69" s="1">
         <v>45870</v>
       </c>
@@ -5778,7 +5778,7 @@
         <v>189458.56091067998</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A70" s="1">
         <v>45901</v>
       </c>
@@ -5798,7 +5798,7 @@
         <v>180385.82079449997</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A71" s="1">
         <v>45931</v>
       </c>
@@ -5818,7 +5818,7 @@
         <v>186189.37231287998</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A72" s="1">
         <v>45962</v>
       </c>
@@ -5838,7 +5838,7 @@
         <v>206545.96854881002</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A73" s="1">
         <v>45992</v>
       </c>
@@ -5858,7 +5858,7 @@
         <v>237422.83153399001</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A74" s="1">
         <v>46023</v>
       </c>
@@ -5878,7 +5878,7 @@
         <v>172090.86346120998</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A75" s="1">
         <v>46054</v>
       </c>
@@ -5898,7 +5898,7 @@
         <v>152599.45469730999</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A76" s="1">
         <v>46082</v>
       </c>
@@ -5918,7 +5918,7 @@
         <v>171057.54617944002</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A77" s="1">
         <v>46113</v>
       </c>
@@ -5946,42 +5946,42 @@
     <tabColor rgb="FFFFC000"/>
   </sheetPr>
   <dimension ref="A1:R77"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="22" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="25.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="25.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" ht="40.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="18" t="s">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="C1" s="18" t="s">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="D1" s="18" t="s">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="E1" s="18" t="s">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="F1" s="17" t="s">
-        <v>54</v>
+        <v>21</v>
       </c>
       <c r="G1" s="3"/>
       <c r="H1" s="3"/>
       <c r="I1" s="3"/>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>43831</v>
       </c>
@@ -6013,7 +6013,7 @@
       <c r="Q2" s="6"/>
       <c r="R2" s="6"/>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>43862</v>
       </c>
@@ -6045,7 +6045,7 @@
       <c r="Q3" s="6"/>
       <c r="R3" s="6"/>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>43891</v>
       </c>
@@ -6077,7 +6077,7 @@
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>43922</v>
       </c>
@@ -6109,7 +6109,7 @@
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>43952</v>
       </c>
@@ -6141,7 +6141,7 @@
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>43983</v>
       </c>
@@ -6173,7 +6173,7 @@
       <c r="Q7" s="6"/>
       <c r="R7" s="6"/>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>44013</v>
       </c>
@@ -6205,7 +6205,7 @@
       <c r="Q8" s="6"/>
       <c r="R8" s="6"/>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>44044</v>
       </c>
@@ -6225,7 +6225,7 @@
         <v>2.0558999999999998</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>44075</v>
       </c>
@@ -6245,7 +6245,7 @@
         <v>2.0558999999999998</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>44105</v>
       </c>
@@ -6265,7 +6265,7 @@
         <v>2.0558999999999998</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>44136</v>
       </c>
@@ -6285,7 +6285,7 @@
         <v>2.0558999999999998</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>44166</v>
       </c>
@@ -6305,7 +6305,7 @@
         <v>2.0558999999999998</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>44197</v>
       </c>
@@ -6325,7 +6325,7 @@
         <v>2.0558999999999998</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>44228</v>
       </c>
@@ -6345,7 +6345,7 @@
         <v>2.0558999999999998</v>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>44256</v>
       </c>
@@ -6365,7 +6365,7 @@
         <v>2.0558999999999998</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>44287</v>
       </c>
@@ -6385,7 +6385,7 @@
         <v>2.0558999999999998</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>44317</v>
       </c>
@@ -6405,7 +6405,7 @@
         <v>2.0558999999999998</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>44348</v>
       </c>
@@ -6425,7 +6425,7 @@
         <v>2.0558999999999998</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>44378</v>
       </c>
@@ -6445,7 +6445,7 @@
         <v>2.0558999999999998</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>44409</v>
       </c>
@@ -6465,7 +6465,7 @@
         <v>2.0558999999999998</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>44440</v>
       </c>
@@ -6485,7 +6485,7 @@
         <v>2.0558999999999998</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>44470</v>
       </c>
@@ -6505,7 +6505,7 @@
         <v>2.0558999999999998</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>44501</v>
       </c>
@@ -6525,7 +6525,7 @@
         <v>2.0558999999999998</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>44531</v>
       </c>
@@ -6545,7 +6545,7 @@
         <v>2.0558999999999998</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>44562</v>
       </c>
@@ -6565,7 +6565,7 @@
         <v>2.0558999999999998</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>44593</v>
       </c>
@@ -6585,7 +6585,7 @@
         <v>2.0558999999999998</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>44621</v>
       </c>
@@ -6605,7 +6605,7 @@
         <v>2.0558999999999998</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>44652</v>
       </c>
@@ -6625,7 +6625,7 @@
         <v>2.0558999999999998</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>44682</v>
       </c>
@@ -6645,7 +6645,7 @@
         <v>2.0558999999999998</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>44713</v>
       </c>
@@ -6665,7 +6665,7 @@
         <v>2.0558999999999998</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>44743</v>
       </c>
@@ -6685,7 +6685,7 @@
         <v>2.0558999999999998</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>44774</v>
       </c>
@@ -6705,7 +6705,7 @@
         <v>2.0558999999999998</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>44805</v>
       </c>
@@ -6725,7 +6725,7 @@
         <v>2.0558999999999998</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <v>44835</v>
       </c>
@@ -6745,7 +6745,7 @@
         <v>2.0558999999999998</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <v>44866</v>
       </c>
@@ -6765,7 +6765,7 @@
         <v>2.0558999999999998</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <v>44896</v>
       </c>
@@ -6785,7 +6785,7 @@
         <v>2.0558999999999998</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <v>44927</v>
       </c>
@@ -6805,7 +6805,7 @@
         <v>2.0558999999999998</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <v>44958</v>
       </c>
@@ -6825,7 +6825,7 @@
         <v>2.0558999999999998</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <v>44986</v>
       </c>
@@ -6845,7 +6845,7 @@
         <v>2.0558999999999998</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
         <v>45017</v>
       </c>
@@ -6865,7 +6865,7 @@
         <v>2.0558999999999998</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
         <v>45047</v>
       </c>
@@ -6885,7 +6885,7 @@
         <v>2.0558999999999998</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
         <v>45078</v>
       </c>
@@ -6905,7 +6905,7 @@
         <v>2.0558999999999998</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
         <v>45108</v>
       </c>
@@ -6925,7 +6925,7 @@
         <v>2.0558999999999998</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" s="1">
         <v>45139</v>
       </c>
@@ -6945,7 +6945,7 @@
         <v>7.0558999999999994</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
         <v>45170</v>
       </c>
@@ -6965,7 +6965,7 @@
         <v>7.0558999999999994</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
         <v>45200</v>
       </c>
@@ -6985,7 +6985,7 @@
         <v>7.0558999999999994</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
         <v>45231</v>
       </c>
@@ -7005,7 +7005,7 @@
         <v>7.0558999999999994</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" s="1">
         <v>45261</v>
       </c>
@@ -7025,7 +7025,7 @@
         <v>7.0558999999999994</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" s="1">
         <v>45292</v>
       </c>
@@ -7045,7 +7045,7 @@
         <v>8.8628999999999998</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" s="1">
         <v>45323</v>
       </c>
@@ -7065,7 +7065,7 @@
         <v>8.8628999999999998</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" s="1">
         <v>45352</v>
       </c>
@@ -7085,7 +7085,7 @@
         <v>8.8628999999999998</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" s="1">
         <v>45383</v>
       </c>
@@ -7105,7 +7105,7 @@
         <v>8.8628999999999998</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54" s="1">
         <v>45413</v>
       </c>
@@ -7125,7 +7125,7 @@
         <v>8.8628999999999998</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55" s="1">
         <v>45444</v>
       </c>
@@ -7145,7 +7145,7 @@
         <v>8.8628999999999998</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56" s="1">
         <v>45474</v>
       </c>
@@ -7165,7 +7165,7 @@
         <v>10.5905</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57" s="1">
         <v>45505</v>
       </c>
@@ -7185,7 +7185,7 @@
         <v>10.5905</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58" s="1">
         <v>45536</v>
       </c>
@@ -7205,7 +7205,7 @@
         <v>10.5905</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59" s="1">
         <v>45566</v>
       </c>
@@ -7225,7 +7225,7 @@
         <v>10.5905</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60" s="1">
         <v>45597</v>
       </c>
@@ -7245,7 +7245,7 @@
         <v>10.5905</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61" s="1">
         <v>45627</v>
       </c>
@@ -7265,7 +7265,7 @@
         <v>10.5905</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62" s="1">
         <v>45658</v>
       </c>
@@ -7285,7 +7285,7 @@
         <v>11.232699999999999</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63" s="1">
         <v>45689</v>
       </c>
@@ -7305,7 +7305,7 @@
         <v>11.232699999999999</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64" s="1">
         <v>45717</v>
       </c>
@@ -7325,7 +7325,7 @@
         <v>11.232699999999999</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A65" s="1">
         <v>45748</v>
       </c>
@@ -7345,7 +7345,7 @@
         <v>11.232699999999999</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A66" s="1">
         <v>45778</v>
       </c>
@@ -7365,7 +7365,7 @@
         <v>11.232699999999999</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A67" s="1">
         <v>45809</v>
       </c>
@@ -7385,7 +7385,7 @@
         <v>11.232699999999999</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A68" s="1">
         <v>45839</v>
       </c>
@@ -7405,7 +7405,7 @@
         <v>12.9968</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A69" s="1">
         <v>45870</v>
       </c>
@@ -7425,7 +7425,7 @@
         <v>12.9968</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A70" s="1">
         <v>45901</v>
       </c>
@@ -7445,7 +7445,7 @@
         <v>12.9968</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A71" s="1">
         <v>45931</v>
       </c>
@@ -7465,7 +7465,7 @@
         <v>12.9968</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A72" s="1">
         <v>45962</v>
       </c>
@@ -7485,7 +7485,7 @@
         <v>12.9968</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A73" s="1">
         <v>45992</v>
       </c>
@@ -7505,7 +7505,7 @@
         <v>12.9968</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A74" s="1">
         <v>46023</v>
       </c>
@@ -7525,7 +7525,7 @@
         <v>13.9</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A75" s="1">
         <v>46054</v>
       </c>
@@ -7545,7 +7545,7 @@
         <v>13.9</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A76" s="1">
         <v>46082</v>
       </c>
@@ -7565,7 +7565,7 @@
         <v>13.9</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A77" s="1">
         <v>46113</v>
       </c>
@@ -7596,36 +7596,36 @@
     <tabColor rgb="FFFFC000"/>
   </sheetPr>
   <dimension ref="A1:S77"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="22" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="18" t="s">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="C1" s="18" t="s">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="D1" s="18" t="s">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="E1" s="3"/>
       <c r="F1" s="3"/>
       <c r="G1" s="3"/>
       <c r="H1" s="3"/>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>43831</v>
       </c>
@@ -7653,7 +7653,7 @@
       <c r="R2" s="6"/>
       <c r="S2" s="6"/>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>43862</v>
       </c>
@@ -7681,7 +7681,7 @@
       <c r="R3" s="6"/>
       <c r="S3" s="6"/>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>43891</v>
       </c>
@@ -7709,7 +7709,7 @@
       <c r="R4" s="6"/>
       <c r="S4" s="6"/>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>43922</v>
       </c>
@@ -7737,7 +7737,7 @@
       <c r="R5" s="6"/>
       <c r="S5" s="6"/>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>43952</v>
       </c>
@@ -7765,7 +7765,7 @@
       <c r="R6" s="6"/>
       <c r="S6" s="6"/>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>43983</v>
       </c>
@@ -7793,7 +7793,7 @@
       <c r="R7" s="6"/>
       <c r="S7" s="6"/>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>44013</v>
       </c>
@@ -7821,7 +7821,7 @@
       <c r="R8" s="6"/>
       <c r="S8" s="6"/>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>44044</v>
       </c>
@@ -7848,7 +7848,7 @@
       <c r="Q9" s="6"/>
       <c r="R9" s="6"/>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>44075</v>
       </c>
@@ -7862,7 +7862,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>44105</v>
       </c>
@@ -7876,7 +7876,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>44136</v>
       </c>
@@ -7890,7 +7890,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>44166</v>
       </c>
@@ -7904,7 +7904,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>44197</v>
       </c>
@@ -7918,7 +7918,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>44228</v>
       </c>
@@ -7932,7 +7932,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>44256</v>
       </c>
@@ -7946,7 +7946,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>44287</v>
       </c>
@@ -7960,7 +7960,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>44317</v>
       </c>
@@ -7974,7 +7974,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>44348</v>
       </c>
@@ -7988,7 +7988,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>44378</v>
       </c>
@@ -8002,7 +8002,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>44409</v>
       </c>
@@ -8016,7 +8016,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>44440</v>
       </c>
@@ -8030,7 +8030,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>44470</v>
       </c>
@@ -8044,7 +8044,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>44501</v>
       </c>
@@ -8058,7 +8058,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>44531</v>
       </c>
@@ -8072,7 +8072,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>44562</v>
       </c>
@@ -8086,7 +8086,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>44593</v>
       </c>
@@ -8100,7 +8100,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>44621</v>
       </c>
@@ -8114,7 +8114,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>44652</v>
       </c>
@@ -8128,7 +8128,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>44682</v>
       </c>
@@ -8142,7 +8142,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>44713</v>
       </c>
@@ -8156,7 +8156,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>44743</v>
       </c>
@@ -8170,7 +8170,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>44774</v>
       </c>
@@ -8184,7 +8184,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>44805</v>
       </c>
@@ -8198,7 +8198,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <v>44835</v>
       </c>
@@ -8212,7 +8212,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <v>44866</v>
       </c>
@@ -8226,7 +8226,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <v>44896</v>
       </c>
@@ -8240,7 +8240,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <v>44927</v>
       </c>
@@ -8254,7 +8254,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <v>44958</v>
       </c>
@@ -8268,7 +8268,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <v>44986</v>
       </c>
@@ -8282,7 +8282,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
         <v>45017</v>
       </c>
@@ -8296,7 +8296,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
         <v>45047</v>
       </c>
@@ -8310,7 +8310,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
         <v>45078</v>
       </c>
@@ -8324,7 +8324,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
         <v>45108</v>
       </c>
@@ -8338,7 +8338,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="1">
         <v>45139</v>
       </c>
@@ -8352,7 +8352,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
         <v>45170</v>
       </c>
@@ -8366,7 +8366,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
         <v>45200</v>
       </c>
@@ -8380,7 +8380,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
         <v>45231</v>
       </c>
@@ -8394,7 +8394,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="1">
         <v>45261</v>
       </c>
@@ -8408,7 +8408,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="1">
         <v>45292</v>
       </c>
@@ -8422,7 +8422,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="1">
         <v>45323</v>
       </c>
@@ -8436,7 +8436,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="1">
         <v>45352</v>
       </c>
@@ -8450,7 +8450,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="1">
         <v>45383</v>
       </c>
@@ -8464,7 +8464,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="1">
         <v>45413</v>
       </c>
@@ -8478,7 +8478,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="1">
         <v>45444</v>
       </c>
@@ -8492,7 +8492,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" s="1">
         <v>45474</v>
       </c>
@@ -8506,7 +8506,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" s="1">
         <v>45505</v>
       </c>
@@ -8520,7 +8520,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" s="1">
         <v>45536</v>
       </c>
@@ -8534,7 +8534,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" s="1">
         <v>45566</v>
       </c>
@@ -8548,7 +8548,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60" s="1">
         <v>45597</v>
       </c>
@@ -8562,7 +8562,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61" s="1">
         <v>45627</v>
       </c>
@@ -8576,7 +8576,7 @@
         <v>53.5</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62" s="1">
         <v>45658</v>
       </c>
@@ -8590,7 +8590,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63" s="1">
         <v>45689</v>
       </c>
@@ -8604,7 +8604,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" s="1">
         <v>45717</v>
       </c>
@@ -8618,7 +8618,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65" s="1">
         <v>45748</v>
       </c>
@@ -8632,7 +8632,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A66" s="1">
         <v>45778</v>
       </c>
@@ -8646,7 +8646,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67" s="1">
         <v>45809</v>
       </c>
@@ -8660,7 +8660,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A68" s="1">
         <v>45839</v>
       </c>
@@ -8674,7 +8674,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69" s="1">
         <v>45870</v>
       </c>
@@ -8688,7 +8688,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A70" s="1">
         <v>45901</v>
       </c>
@@ -8702,7 +8702,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71" s="1">
         <v>45931</v>
       </c>
@@ -8716,7 +8716,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A72" s="1">
         <v>45962</v>
       </c>
@@ -8730,7 +8730,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A73" s="1">
         <v>45992</v>
       </c>
@@ -8744,7 +8744,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A74" s="1">
         <v>46023</v>
       </c>
@@ -8758,7 +8758,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A75" s="1">
         <v>46054</v>
       </c>
@@ -8772,7 +8772,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A76" s="1">
         <v>46082</v>
       </c>
@@ -8786,7 +8786,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A77" s="1">
         <v>46113</v>
       </c>
@@ -8811,44 +8811,44 @@
     <tabColor rgb="FFFFC000"/>
   </sheetPr>
   <dimension ref="A1:T99"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.28515625" customWidth="1"/>
+    <col min="1" max="1" width="11.33203125" customWidth="1"/>
     <col min="2" max="4" width="22" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="22" style="6" customWidth="1"/>
     <col min="6" max="7" width="22" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" ht="41.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="18" t="s">
-        <v>51</v>
+        <v>18</v>
       </c>
       <c r="C1" s="18" t="s">
-        <v>57</v>
+        <v>24</v>
       </c>
       <c r="D1" s="18" t="s">
-        <v>58</v>
+        <v>25</v>
       </c>
       <c r="E1" s="18" t="s">
-        <v>59</v>
+        <v>26</v>
       </c>
       <c r="F1" s="18" t="s">
-        <v>60</v>
+        <v>27</v>
       </c>
       <c r="G1" s="18" t="s">
-        <v>61</v>
+        <v>28</v>
       </c>
       <c r="H1" s="18" t="s">
-        <v>62</v>
+        <v>29</v>
       </c>
       <c r="I1" s="3"/>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>43831</v>
       </c>
@@ -8886,7 +8886,7 @@
       <c r="S2" s="6"/>
       <c r="T2" s="6"/>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>43862</v>
       </c>
@@ -8924,7 +8924,7 @@
       <c r="S3" s="6"/>
       <c r="T3" s="6"/>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>43891</v>
       </c>
@@ -8962,7 +8962,7 @@
       <c r="S4" s="6"/>
       <c r="T4" s="6"/>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>43922</v>
       </c>
@@ -9000,7 +9000,7 @@
       <c r="S5" s="6"/>
       <c r="T5" s="6"/>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>43952</v>
       </c>
@@ -9038,7 +9038,7 @@
       <c r="S6" s="6"/>
       <c r="T6" s="6"/>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>43983</v>
       </c>
@@ -9076,7 +9076,7 @@
       <c r="S7" s="6"/>
       <c r="T7" s="6"/>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>44013</v>
       </c>
@@ -9114,7 +9114,7 @@
       <c r="S8" s="6"/>
       <c r="T8" s="6"/>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>44044</v>
       </c>
@@ -9152,7 +9152,7 @@
       <c r="S9" s="6"/>
       <c r="T9" s="6"/>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>44075</v>
       </c>
@@ -9179,7 +9179,7 @@
       </c>
       <c r="I10" s="6"/>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>44105</v>
       </c>
@@ -9205,7 +9205,7 @@
         <v>0.66946962821857614</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>44136</v>
       </c>
@@ -9231,7 +9231,7 @@
         <v>0.69280397010018424</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>44166</v>
       </c>
@@ -9257,7 +9257,7 @@
         <v>0.64952604026384775</v>
       </c>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>44197</v>
       </c>
@@ -9283,7 +9283,7 @@
         <v>0.56906458759236178</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>44228</v>
       </c>
@@ -9309,7 +9309,7 @@
         <v>0.59347225922498614</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>44256</v>
       </c>
@@ -9335,7 +9335,7 @@
         <v>0.63505315158124565</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>44287</v>
       </c>
@@ -9361,7 +9361,7 @@
         <v>0.61820261520809938</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>44317</v>
       </c>
@@ -9387,7 +9387,7 @@
         <v>0.63267228364355255</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>44348</v>
       </c>
@@ -9413,7 +9413,7 @@
         <v>0.64174513015046586</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>44378</v>
       </c>
@@ -9439,7 +9439,7 @@
         <v>0.64046377461732085</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>44409</v>
       </c>
@@ -9465,7 +9465,7 @@
         <v>0.65840804813446285</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>44440</v>
       </c>
@@ -9491,7 +9491,7 @@
         <v>0.66161480719372323</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>44470</v>
       </c>
@@ -9517,7 +9517,7 @@
         <v>0.68130121070425864</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>44501</v>
       </c>
@@ -9543,7 +9543,7 @@
         <v>0.7378646514877093</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>44531</v>
       </c>
@@ -9569,7 +9569,7 @@
         <v>0.80615377005806721</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>44562</v>
       </c>
@@ -9595,7 +9595,7 @@
         <v>0.58616917172721461</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>44593</v>
       </c>
@@ -9621,7 +9621,7 @@
         <v>0.66526380110531913</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>44621</v>
       </c>
@@ -9647,7 +9647,7 @@
         <v>0.72402531235251166</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>44652</v>
       </c>
@@ -9673,7 +9673,7 @@
         <v>0.75029772781712178</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>44682</v>
       </c>
@@ -9699,7 +9699,7 @@
         <v>0.80650534821143494</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>44713</v>
       </c>
@@ -9725,7 +9725,7 @@
         <v>0.81331393663791218</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>44743</v>
       </c>
@@ -9751,7 +9751,7 @@
         <v>0.79850192767313266</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>44774</v>
       </c>
@@ -9777,7 +9777,7 @@
         <v>0.85350385264845341</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>44805</v>
       </c>
@@ -9803,7 +9803,7 @@
         <v>0.85146603765573237</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <v>44835</v>
       </c>
@@ -9829,7 +9829,7 @@
         <v>0.8476981109374131</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <v>44866</v>
       </c>
@@ -9855,7 +9855,7 @@
         <v>0.85121274742769859</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <v>44896</v>
       </c>
@@ -9881,7 +9881,7 @@
         <v>0.82924203457039847</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <v>44927</v>
       </c>
@@ -9907,7 +9907,7 @@
         <v>0.71701974222474285</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <v>44958</v>
       </c>
@@ -9933,7 +9933,7 @@
         <v>0.72757995822606214</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <v>44986</v>
       </c>
@@ -9959,7 +9959,7 @@
         <v>0.75767867262018351</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
         <v>45017</v>
       </c>
@@ -9985,7 +9985,7 @@
         <v>0.80906878765619117</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
         <v>45047</v>
       </c>
@@ -10011,7 +10011,7 @@
         <v>0.77254632638398868</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
         <v>45078</v>
       </c>
@@ -10037,7 +10037,7 @@
         <v>0.80232271445519665</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
         <v>45108</v>
       </c>
@@ -10063,7 +10063,7 @@
         <v>0.80593678389047185</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" s="1">
         <v>45139</v>
       </c>
@@ -10089,7 +10089,7 @@
         <v>0.83534286881645425</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
         <v>45170</v>
       </c>
@@ -10115,7 +10115,7 @@
         <v>0.81819851324342685</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
         <v>45200</v>
       </c>
@@ -10141,7 +10141,7 @@
         <v>0.80348808609799771</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
         <v>45231</v>
       </c>
@@ -10167,7 +10167,7 @@
         <v>0.79072952944489516</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" s="1">
         <v>45261</v>
       </c>
@@ -10193,7 +10193,7 @@
         <v>0.8212325759998208</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" s="1">
         <v>45292</v>
       </c>
@@ -10219,7 +10219,7 @@
         <v>0.48678955790188078</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" s="1">
         <v>45323</v>
       </c>
@@ -10245,7 +10245,7 @@
         <v>0.63737479850595613</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" s="1">
         <v>45352</v>
       </c>
@@ -10271,7 +10271,7 @@
         <v>0.67310571412954234</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" s="1">
         <v>45383</v>
       </c>
@@ -10297,7 +10297,7 @@
         <v>0.68946080492832051</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" s="1">
         <v>45413</v>
       </c>
@@ -10323,7 +10323,7 @@
         <v>0.72100581918979445</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" s="1">
         <v>45444</v>
       </c>
@@ -10349,7 +10349,7 @@
         <v>0.72896756954521713</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" s="1">
         <v>45474</v>
       </c>
@@ -10375,7 +10375,7 @@
         <v>0.71481013167491647</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" s="1">
         <v>45505</v>
       </c>
@@ -10401,7 +10401,7 @@
         <v>0.76597699706612299</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" s="1">
         <v>45536</v>
       </c>
@@ -10427,7 +10427,7 @@
         <v>0.74517192919644293</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" s="1">
         <v>45566</v>
       </c>
@@ -10453,7 +10453,7 @@
         <v>0.758631531601487</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" s="1">
         <v>45597</v>
       </c>
@@ -10479,7 +10479,7 @@
         <v>0.78587001321917482</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" s="1">
         <v>45627</v>
       </c>
@@ -10505,7 +10505,7 @@
         <v>0.77828809877849081</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" s="1">
         <v>45658</v>
       </c>
@@ -10531,7 +10531,7 @@
         <v>0.75929071926636771</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63" s="1">
         <v>45689</v>
       </c>
@@ -10557,7 +10557,7 @@
         <v>0.7668416943671279</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64" s="1">
         <v>45717</v>
       </c>
@@ -10583,7 +10583,7 @@
         <v>0.76948062419495578</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65" s="1">
         <v>45748</v>
       </c>
@@ -10609,7 +10609,7 @@
         <v>0.76693452525931238</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66" s="1">
         <v>45778</v>
       </c>
@@ -10635,7 +10635,7 @@
         <v>0.77032817615930982</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67" s="1">
         <v>45809</v>
       </c>
@@ -10661,7 +10661,7 @@
         <v>0.77567602239150268</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68" s="1">
         <v>45839</v>
       </c>
@@ -10687,7 +10687,7 @@
         <v>0.78152209431485731</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A69" s="1">
         <v>45870</v>
       </c>
@@ -10713,7 +10713,7 @@
         <v>0.80730510882003381</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70" s="1">
         <v>45901</v>
       </c>
@@ -10739,7 +10739,7 @@
         <v>0.80804950610904491</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A71" s="1">
         <v>45931</v>
       </c>
@@ -10765,7 +10765,7 @@
         <v>0.78363648544681608</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A72" s="1">
         <v>45962</v>
       </c>
@@ -10791,7 +10791,7 @@
         <v>0.78343492552335614</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A73" s="1">
         <v>45992</v>
       </c>
@@ -10817,7 +10817,7 @@
         <v>0.79886908493396391</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A74" s="1">
         <v>46023</v>
       </c>
@@ -10843,7 +10843,7 @@
         <v>0.76096560899773069</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A75" s="1">
         <v>46054</v>
       </c>
@@ -10869,7 +10869,7 @@
         <v>0.79029933541135433</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A76" s="1">
         <v>46082</v>
       </c>
@@ -10895,7 +10895,7 @@
         <v>0.81984991199856805</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A77" s="1">
         <v>46113</v>
       </c>
@@ -10921,133 +10921,133 @@
         <v>0.80729107742745132</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C78" s="10"/>
       <c r="D78" s="10"/>
       <c r="F78" s="10"/>
       <c r="G78" s="10"/>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C79" s="10"/>
       <c r="D79" s="10"/>
       <c r="F79" s="10"/>
       <c r="G79" s="10"/>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C80" s="10"/>
       <c r="D80" s="10"/>
       <c r="F80" s="10"/>
       <c r="G80" s="10"/>
     </row>
-    <row r="81" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="81" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C81" s="10"/>
       <c r="D81" s="10"/>
       <c r="F81" s="10"/>
       <c r="G81" s="10"/>
     </row>
-    <row r="82" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="82" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C82" s="10"/>
       <c r="D82" s="10"/>
       <c r="F82" s="10"/>
       <c r="G82" s="10"/>
     </row>
-    <row r="83" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="83" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C83" s="10"/>
       <c r="D83" s="10"/>
       <c r="F83" s="10"/>
       <c r="G83" s="10"/>
     </row>
-    <row r="84" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="84" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C84" s="10"/>
       <c r="D84" s="10"/>
       <c r="F84" s="10"/>
       <c r="G84" s="10"/>
     </row>
-    <row r="85" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="85" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C85" s="10"/>
       <c r="D85" s="10"/>
       <c r="F85" s="10"/>
       <c r="G85" s="10"/>
     </row>
-    <row r="86" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="86" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C86" s="10"/>
       <c r="D86" s="10"/>
       <c r="F86" s="10"/>
       <c r="G86" s="10"/>
     </row>
-    <row r="87" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="87" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C87" s="10"/>
       <c r="D87" s="10"/>
       <c r="F87" s="10"/>
       <c r="G87" s="10"/>
     </row>
-    <row r="88" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="88" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C88" s="10"/>
       <c r="D88" s="10"/>
       <c r="F88" s="10"/>
       <c r="G88" s="10"/>
     </row>
-    <row r="89" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="89" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C89" s="10"/>
       <c r="D89" s="10"/>
       <c r="F89" s="10"/>
       <c r="G89" s="10"/>
     </row>
-    <row r="90" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="90" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C90" s="10"/>
       <c r="D90" s="10"/>
       <c r="F90" s="10"/>
       <c r="G90" s="10"/>
     </row>
-    <row r="91" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="91" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C91" s="10"/>
       <c r="D91" s="10"/>
       <c r="F91" s="10"/>
       <c r="G91" s="10"/>
     </row>
-    <row r="92" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="92" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C92" s="10"/>
       <c r="D92" s="10"/>
       <c r="F92" s="10"/>
       <c r="G92" s="10"/>
     </row>
-    <row r="93" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="93" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C93" s="10"/>
       <c r="D93" s="10"/>
       <c r="F93" s="10"/>
       <c r="G93" s="10"/>
     </row>
-    <row r="94" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="94" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C94" s="10"/>
       <c r="D94" s="10"/>
       <c r="F94" s="10"/>
       <c r="G94" s="10"/>
     </row>
-    <row r="95" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="95" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C95" s="10"/>
       <c r="D95" s="10"/>
       <c r="F95" s="10"/>
       <c r="G95" s="10"/>
     </row>
-    <row r="96" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="96" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C96" s="10"/>
       <c r="D96" s="10"/>
       <c r="F96" s="10"/>
       <c r="G96" s="10"/>
     </row>
-    <row r="97" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="97" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C97" s="10"/>
       <c r="D97" s="10"/>
       <c r="F97" s="10"/>
       <c r="G97" s="10"/>
     </row>
-    <row r="98" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="98" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C98" s="10"/>
       <c r="D98" s="10"/>
       <c r="F98" s="10"/>
       <c r="G98" s="10"/>
     </row>
-    <row r="99" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="99" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C99" s="10"/>
       <c r="D99" s="10"/>
       <c r="F99" s="10"/>
